--- a/reports/Debug-snowbowl-20260106/For Winter Ending (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-snowbowl-20260106/For Winter Ending (Prior Year)_Payroll_history.xlsx
@@ -31,6 +31,21 @@
     <t>D9008</t>
   </si>
   <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D9007</t>
+  </si>
+  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -46,21 +61,6 @@
     <t>D7010</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5820</t>
-  </si>
-  <si>
-    <t>D9007</t>
-  </si>
-  <si>
     <t>D1200</t>
   </si>
   <si>
@@ -76,6 +76,24 @@
     <t>D8060</t>
   </si>
   <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>D9000</t>
+  </si>
+  <si>
+    <t>D9009</t>
+  </si>
+  <si>
     <t>D1100</t>
   </si>
   <si>
@@ -95,24 +113,6 @@
   </si>
   <si>
     <t>D8040</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D9000</t>
-  </si>
-  <si>
-    <t>D9009</t>
   </si>
   <si>
     <t>D1030</t>
@@ -575,7 +575,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>60117.09</v>
+        <v>86480.35</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -583,7 +583,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>41016.49</v>
+        <v>24708.56</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>13974.86</v>
+        <v>51081.21</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -599,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>27708.01</v>
+        <v>4749.46</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -607,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>18636.61</v>
+        <v>6921.88</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -615,7 +615,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>86480.35</v>
+        <v>60117.09</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -623,7 +623,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>24708.56</v>
+        <v>41016.49</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -631,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>51081.21</v>
+        <v>13974.86</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -639,7 +639,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>4749.46</v>
+        <v>27708.01</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -647,7 +647,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>6921.88</v>
+        <v>18636.61</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>43949.57</v>
+        <v>406220.35</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -703,7 +703,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>111769.36</v>
+        <v>12491.76</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>62211.51</v>
+        <v>62379.68</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -719,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>25606.39</v>
+        <v>50147.31</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -727,7 +727,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>48247.93</v>
+        <v>220.41</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -735,7 +735,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>19559.76</v>
+        <v>186.27</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -743,7 +743,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>35247.12</v>
+        <v>43949.57</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -751,7 +751,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>406220.35</v>
+        <v>111769.36</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -759,7 +759,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>12491.76</v>
+        <v>62211.51</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -767,7 +767,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>62379.68</v>
+        <v>25606.39</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -775,7 +775,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>50147.31</v>
+        <v>48247.93</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -783,7 +783,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>220.41</v>
+        <v>19559.76</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -791,7 +791,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>186.27</v>
+        <v>35247.12</v>
       </c>
     </row>
     <row r="34" spans="1:2">
